--- a/01-INTRO/M03/bus311-intro-m03-l01-factset-cat-activity.xlsx
+++ b/01-INTRO/M03/bus311-intro-m03-l01-factset-cat-activity.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10802"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bethanyevittsair2/Documents/GitHub/BUS311-Corporate_Finance/01-INTRO/M03/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AAEF16C-728A-F742-8564-2EBCEBE747BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5ACFB5EC-5A5D-8D41-9947-25213F0D536D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3920" yWindow="1700" windowWidth="29760" windowHeight="20040" xr2:uid="{0347E573-4F0D-418B-B17B-965F803E2356}"/>
+    <workbookView xWindow="0" yWindow="580" windowWidth="25600" windowHeight="15260" xr2:uid="{0347E573-4F0D-418B-B17B-965F803E2356}"/>
   </bookViews>
   <sheets>
     <sheet name="Student CAT Wksht" sheetId="1" r:id="rId1"/>
@@ -1673,8 +1673,8 @@
   <dimension ref="A1:N38"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="29" customWidth="1"/>
-    <col min="2" max="2" width="25.6640625" customWidth="1"/>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="34.5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="51.6640625" customWidth="1"/>
     <col min="5" max="7" width="10.83203125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
